--- a/exports/visitors.xlsx
+++ b/exports/visitors.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -84,6 +84,18 @@
   </si>
   <si>
     <t>2026-06-08T13:14:21.885137</t>
+  </si>
+  <si>
+    <t>Ravi</t>
+  </si>
+  <si>
+    <t>9876543915</t>
+  </si>
+  <si>
+    <t>Rajesh@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-06-08T16:12:19.070162</t>
   </si>
 </sst>
 </file>
@@ -134,7 +146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="2.71875" customWidth="true" bestFit="true"/>
@@ -261,6 +273,29 @@
         <v>23</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/exports/visitors.xlsx
+++ b/exports/visitors.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -35,6 +35,9 @@
     <t>Visit Time</t>
   </si>
   <si>
+    <t>PhotoURL</t>
+  </si>
+  <si>
     <t>Ravi Kumar</t>
   </si>
   <si>
@@ -53,6 +56,9 @@
     <t>2026-06-04T13:20:24.943653</t>
   </si>
   <si>
+    <t>https://cloudinary.com/images/photo1.jpg</t>
+  </si>
+  <si>
     <t>9876543910</t>
   </si>
   <si>
@@ -96,6 +102,15 @@
   </si>
   <si>
     <t>2026-06-08T16:12:19.070162</t>
+  </si>
+  <si>
+    <t>9876543916</t>
+  </si>
+  <si>
+    <t>Rajes@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-06-10T09:51:24.170919</t>
   </si>
 </sst>
 </file>
@@ -146,7 +161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="2.71875" customWidth="true" bestFit="true"/>
@@ -156,6 +171,7 @@
     <col min="5" max="5" width="10.03125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="9.0234375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="24.65234375" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="35.4453125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -180,28 +196,34 @@
       <c r="G1" t="s" s="1">
         <v>6</v>
       </c>
+      <c r="H1" t="s" s="1">
+        <v>7</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -209,22 +231,25 @@
         <v>2.0</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -232,22 +257,25 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -255,22 +283,25 @@
         <v>4.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -278,22 +309,51 @@
         <v>5.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="E6" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>27</v>
+      <c r="C7" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/exports/visitors.xlsx
+++ b/exports/visitors.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -32,25 +32,55 @@
     <t>Visit Time</t>
   </si>
   <si>
-    <t>Photo Stored</t>
-  </si>
-  <si>
-    <t>Gangadhar Hosamani</t>
-  </si>
-  <si>
-    <t>8096533792</t>
-  </si>
-  <si>
-    <t>Ganga@gmail.com</t>
+    <t>Photo Link</t>
+  </si>
+  <si>
+    <t>ganga</t>
+  </si>
+  <si>
+    <t>9876543212</t>
+  </si>
+  <si>
+    <t>ganga@gmail.com</t>
   </si>
   <si>
     <t>INTERVIEW</t>
   </si>
   <si>
-    <t>2026-06-12T13:52:18.325266</t>
-  </si>
-  <si>
-    <t>Yes</t>
+    <t>2026-06-13T11:03:41.309875</t>
+  </si>
+  <si>
+    <t>View Photo</t>
+  </si>
+  <si>
+    <t>gangadhar</t>
+  </si>
+  <si>
+    <t>9876543213</t>
+  </si>
+  <si>
+    <t>gangadhar@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-06-13T11:08:59.968550</t>
+  </si>
+  <si>
+    <t>9876543214</t>
+  </si>
+  <si>
+    <t>gangadha@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-06-13T19:19:10.888762</t>
+  </si>
+  <si>
+    <t>9876543215</t>
+  </si>
+  <si>
+    <t>gangadhs@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-06-13T19:19:38.978969</t>
   </si>
 </sst>
 </file>
@@ -58,7 +88,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -70,6 +100,12 @@
       <name val="Calibri"/>
       <sz val="11.0"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <u val="single"/>
+      <color indexed="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,25 +128,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="2.71875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="18.1796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="9.421875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="16.09765625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="19.48828125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="10.03125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="24.65234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="11.73828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="10.20703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -155,11 +192,86 @@
       <c r="F2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s" s="2">
         <v>12</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1"/>
+    <hyperlink ref="G3" r:id="rId2"/>
+    <hyperlink ref="G4" r:id="rId3"/>
+    <hyperlink ref="G5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/exports/visitors.xlsx
+++ b/exports/visitors.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>ID</t>
   </si>
@@ -35,52 +35,22 @@
     <t>Photo Link</t>
   </si>
   <si>
-    <t>ganga</t>
+    <t>Test User</t>
   </si>
   <si>
-    <t>9876543212</t>
+    <t>9876543210</t>
   </si>
   <si>
-    <t>ganga@gmail.com</t>
+    <t>test123@gmail.com</t>
   </si>
   <si>
-    <t>INTERVIEW</t>
+    <t>MEETING</t>
   </si>
   <si>
-    <t>2026-06-13T11:03:41.309875</t>
+    <t>2026-06-17T13:45:36.782648</t>
   </si>
   <si>
     <t>View Photo</t>
-  </si>
-  <si>
-    <t>gangadhar</t>
-  </si>
-  <si>
-    <t>9876543213</t>
-  </si>
-  <si>
-    <t>gangadhar@gmail.com</t>
-  </si>
-  <si>
-    <t>2026-06-13T11:08:59.968550</t>
-  </si>
-  <si>
-    <t>9876543214</t>
-  </si>
-  <si>
-    <t>gangadha@gmail.com</t>
-  </si>
-  <si>
-    <t>2026-06-13T19:19:10.888762</t>
-  </si>
-  <si>
-    <t>9876543215</t>
-  </si>
-  <si>
-    <t>gangadhs@gmail.com</t>
-  </si>
-  <si>
-    <t>2026-06-13T19:19:38.978969</t>
   </si>
 </sst>
 </file>
@@ -138,14 +108,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="2.71875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="9.421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="8.4609375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="19.48828125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="10.03125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="17.07421875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="8.51953125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="24.65234375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="10.20703125" customWidth="true" bestFit="true"/>
   </cols>
@@ -196,81 +166,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
-    <hyperlink ref="G3" r:id="rId2"/>
-    <hyperlink ref="G4" r:id="rId3"/>
-    <hyperlink ref="G5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/exports/visitors.xlsx
+++ b/exports/visitors.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>ID</t>
   </si>
@@ -32,25 +32,34 @@
     <t>Visit Time</t>
   </si>
   <si>
-    <t>Photo Link</t>
+    <t>Photo</t>
+  </si>
+  <si>
+    <t>Open Photo</t>
   </si>
   <si>
     <t>Test User</t>
   </si>
   <si>
+    <t>9876543211</t>
+  </si>
+  <si>
+    <t>test12@gmail.com</t>
+  </si>
+  <si>
+    <t>MEETING</t>
+  </si>
+  <si>
+    <t>2026-06-18T10:03:45.664590</t>
+  </si>
+  <si>
     <t>9876543210</t>
   </si>
   <si>
     <t>test123@gmail.com</t>
   </si>
   <si>
-    <t>MEETING</t>
-  </si>
-  <si>
-    <t>2026-06-17T13:45:36.782648</t>
-  </si>
-  <si>
-    <t>View Photo</t>
+    <t>2026-06-18T10:32:16.998767</t>
   </si>
 </sst>
 </file>
@@ -106,18 +115,100 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="533530" cy="1016000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="533530" cy="1016000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="7" max="7" width="15.0" customWidth="true"/>
+    <col min="8" max="8" width="15.0" customWidth="true"/>
     <col min="1" max="1" width="2.71875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="8.4609375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.9296875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="17.07421875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="8.51953125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="24.65234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.20703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -142,34 +233,62 @@
       <c r="G1" t="s" s="1">
         <v>6</v>
       </c>
+      <c r="H1" t="s" s="1">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="B2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s" s="2">
         <v>7</v>
       </c>
-      <c r="C2" t="s" s="0">
+    </row>
+    <row r="3" ht="80.0" customHeight="true">
+      <c r="A3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s" s="0">
+      <c r="C3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="G2" t="s" s="2">
-        <v>12</v>
+      <c r="F3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1"/>
+    <hyperlink ref="H2" r:id="rId2"/>
+    <hyperlink ref="H3" r:id="rId3"/>
   </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/exports/visitors.xlsx
+++ b/exports/visitors.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
-  <si>
-    <t>ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+  <si>
+    <t>SL/NO</t>
+  </si>
+  <si>
+    <t>Visitor_ID</t>
   </si>
   <si>
     <t>Name</t>
@@ -35,31 +38,52 @@
     <t>Photo</t>
   </si>
   <si>
-    <t>Open Photo</t>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>1091275235</t>
+  </si>
+  <si>
+    <t>test1@gmail.com</t>
+  </si>
+  <si>
+    <t>MEETING</t>
+  </si>
+  <si>
+    <t>2026-06-18T10:03:45.664590</t>
   </si>
   <si>
     <t>Test User</t>
   </si>
   <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>test123@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-06-18T10:32:16.998767</t>
+  </si>
+  <si>
+    <t>Gangu</t>
+  </si>
+  <si>
     <t>9876543211</t>
   </si>
   <si>
-    <t>test12@gmail.com</t>
-  </si>
-  <si>
-    <t>MEETING</t>
-  </si>
-  <si>
-    <t>2026-06-18T10:03:45.664590</t>
-  </si>
-  <si>
-    <t>9876543210</t>
-  </si>
-  <si>
-    <t>test123@gmail.com</t>
-  </si>
-  <si>
-    <t>2026-06-18T10:32:16.998767</t>
+    <t>test13@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-06-19T13:13:47.494448</t>
+  </si>
+  <si>
+    <t>9876543123</t>
+  </si>
+  <si>
+    <t>test143@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-06-20T10:18:59.653183</t>
   </si>
 </sst>
 </file>
@@ -67,7 +91,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -79,12 +103,6 @@
       <name val="Calibri"/>
       <sz val="11.0"/>
       <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <u val="single"/>
-      <color indexed="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -107,10 +125,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -119,13 +136,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -157,13 +174,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -193,22 +210,97 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="533530" cy="1016000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="533530" cy="1016000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
+    <col min="1" max="1" width="6.1953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="9.0703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="8.4609375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="17.07421875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="8.51953125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="15.0" customWidth="true"/>
-    <col min="8" max="8" width="15.0" customWidth="true"/>
-    <col min="1" max="1" width="2.71875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="8.4609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="17.07421875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="8.51953125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="24.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -239,33 +331,33 @@
     </row>
     <row r="2" ht="80.0" customHeight="true">
       <c r="A2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="B2" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="D2" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="E2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="F2" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="G2" t="s" s="0">
         <v>12</v>
-      </c>
-      <c r="H2" t="s" s="2">
-        <v>7</v>
       </c>
     </row>
     <row r="3" ht="80.0" customHeight="true">
       <c r="A3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B3" t="n" s="0">
         <v>3.0</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>8</v>
       </c>
       <c r="C3" t="s" s="0">
         <v>13</v>
@@ -274,20 +366,62 @@
         <v>14</v>
       </c>
       <c r="E3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>7</v>
+      <c r="G3" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="80.0" customHeight="true">
+      <c r="A4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="80.0" customHeight="true">
+      <c r="A5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H2" r:id="rId2"/>
-    <hyperlink ref="H3" r:id="rId3"/>
-  </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>
